--- a/result_detail.xlsx
+++ b/result_detail.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入结果明细" sheetId="1" r:id="R410e667072644adb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入结果明细" sheetId="1" r:id="R822f83d0b2594491"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -128,9 +128,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -143,12 +143,58 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="dk1"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="accent1"/>
-        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
+                <a:satMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
+                <a:satMod val="110000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="12700">
@@ -273,7 +319,7 @@
         <x:v>主续订单</x:v>
       </x:c>
       <x:c r="H1" s="8" t="str">
-        <x:v>总融金额</x:v>
+        <x:v>债权金额</x:v>
       </x:c>
       <x:c r="I1" s="8" t="str">
         <x:v>逾期天数</x:v>

--- a/result_detail.xlsx
+++ b/result_detail.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入结果明细" sheetId="1" r:id="R822f83d0b2594491"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入结果明细" sheetId="1" r:id="Rf851c5feae554515"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -471,9 +471,48 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="B5" s="10"/>
-      <x:c r="D5" s="10"/>
-      <x:c r="H5" s="11"/>
+      <x:c r="A5" t="str">
+        <x:v>创新</x:v>
+      </x:c>
+      <x:c r="B5" s="10" t="str">
+        <x:v>DR202606100001</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>创新租赁旧合同批次01</x:v>
+      </x:c>
+      <x:c r="D5" s="10" t="str">
+        <x:v>26012915050167612331</x:v>
+      </x:c>
+      <x:c r="E5" t="str">
+        <x:v>周强</x:v>
+      </x:c>
+      <x:c r="F5" t="str">
+        <x:v>租赁</x:v>
+      </x:c>
+      <x:c r="G5" t="str">
+        <x:v>主订单</x:v>
+      </x:c>
+      <x:c r="H5" s="11" t="n">
+        <x:v>8650</x:v>
+      </x:c>
+      <x:c r="I5" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="J5" t="str">
+        <x:v>阻断失败</x:v>
+      </x:c>
+      <x:c r="K5" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L5" t="str">
+        <x:v>重复导入：该订单已在批次DR202606080003（创新租赁旧合同批次00）导入落库；同一批资产多次导入时，以首次导入数据为准，本批次不能重复导入或自动覆盖。</x:v>
+      </x:c>
+      <x:c r="M5" t="str">
+        <x:v>请到首次导入批次DR202606080003查看该订单；如需更正，按原批次处理或走批量补传/更正流程。</x:v>
+      </x:c>
+      <x:c r="N5" t="str">
+        <x:v>2026-06-10 20:15:32</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="B6" s="10"/>
@@ -5450,6 +5489,50 @@
       <x:c r="D1000" s="10"/>
       <x:c r="H1000" s="11"/>
     </x:row>
+    <x:row r="1001">
+      <x:c r="A1001" t="str">
+        <x:v>创新</x:v>
+      </x:c>
+      <x:c r="B1001" t="str">
+        <x:v>DR202606100001</x:v>
+      </x:c>
+      <x:c r="C1001" t="str">
+        <x:v>创新租赁旧合同批次01</x:v>
+      </x:c>
+      <x:c r="D1001" t="str">
+        <x:v>26012915050167612331</x:v>
+      </x:c>
+      <x:c r="E1001" t="str">
+        <x:v>周强</x:v>
+      </x:c>
+      <x:c r="F1001" t="str">
+        <x:v>租赁</x:v>
+      </x:c>
+      <x:c r="G1001" t="str">
+        <x:v>主订单</x:v>
+      </x:c>
+      <x:c r="H1001" t="n">
+        <x:v>8650</x:v>
+      </x:c>
+      <x:c r="I1001" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="J1001" t="str">
+        <x:v>阻断失败</x:v>
+      </x:c>
+      <x:c r="K1001" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L1001" t="str">
+        <x:v>同一批资产已在批次 DR202606080003 导入落库，以第一次导入数据为准，本批次不能重复导入或自动覆盖。</x:v>
+      </x:c>
+      <x:c r="M1001" t="str">
+        <x:v>请到首次导入批次查看该订单；如需更正，按原批次处理或走批量补传/更正流程。</x:v>
+      </x:c>
+      <x:c r="N1001" t="str">
+        <x:v>2026-06-10 20:15:32</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/result_detail.xlsx
+++ b/result_detail.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入结果明细" sheetId="1" r:id="Re5f6e7f229ed4836"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败分类说明" sheetId="2" r:id="R2ca5f2b09b9042ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="一期口径说明" sheetId="3" r:id="R809f876134d241ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入结果明细" sheetId="1" r:id="R85d45ad1527c4435"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败分类说明" sheetId="2" r:id="R9678838870e94822"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="一期口径说明" sheetId="3" r:id="Rc72602e2cbf545a9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -331,8 +331,7 @@
     <x:col min="12" max="12" width="27" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="42" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="14" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="34" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="20" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -379,9 +378,6 @@
         <x:v>是否阻断导入</x:v>
       </x:c>
       <x:c r="O1" s="7" t="str">
-        <x:v>处理建议</x:v>
-      </x:c>
-      <x:c r="P1" s="7" t="str">
         <x:v>导入时间</x:v>
       </x:c>
     </x:row>
@@ -423,15 +419,12 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="M2" s="10" t="str">
-        <x:v>字段校验通过，已生成待委外案件</x:v>
+        <x:v>字段校验通过，案件已生成并生效，已进入待委外队列</x:v>
       </x:c>
       <x:c r="N2" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="O2" s="10" t="str">
-        <x:v>无需处理</x:v>
-      </x:c>
-      <x:c r="P2" s="12" t="str">
+      <x:c r="O2" s="12" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
@@ -476,10 +469,7 @@
       <x:c r="N3" s="11" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="O3" s="10" t="str">
-        <x:v>补充债权金额后重新导入</x:v>
-      </x:c>
-      <x:c r="P3" s="12" t="str">
+      <x:c r="O3" s="12" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
@@ -526,10 +516,7 @@
       <x:c r="N4" s="11" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="O4" s="10" t="str">
-        <x:v>修正身份证号后重新导入</x:v>
-      </x:c>
-      <x:c r="P4" s="12" t="str">
+      <x:c r="O4" s="12" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
@@ -576,10 +563,7 @@
       <x:c r="N5" s="11" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="O5" s="10" t="str">
-        <x:v>修正为大于等于0的金额后重新导入</x:v>
-      </x:c>
-      <x:c r="P5" s="12" t="str">
+      <x:c r="O5" s="12" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
@@ -626,10 +610,7 @@
       <x:c r="N6" s="11" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="O6" s="10" t="str">
-        <x:v>按模板枚举填写后重新导入</x:v>
-      </x:c>
-      <x:c r="P6" s="12" t="str">
+      <x:c r="O6" s="12" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
@@ -676,10 +657,7 @@
       <x:c r="N7" s="11" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="O7" s="10" t="str">
-        <x:v>补充主订单或修正父订单编号后重新导入</x:v>
-      </x:c>
-      <x:c r="P7" s="12" t="str">
+      <x:c r="O7" s="12" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
@@ -726,10 +704,7 @@
       <x:c r="N8" s="11" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="O8" s="10" t="str">
-        <x:v>核对历史批次，如需修正请走后续更正流程</x:v>
-      </x:c>
-      <x:c r="P8" s="12" t="str">
+      <x:c r="O8" s="12" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
@@ -776,10 +751,7 @@
       <x:c r="N9" s="11" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="O9" s="10" t="str">
-        <x:v>确认订单状态，剔除后重新导入</x:v>
-      </x:c>
-      <x:c r="P9" s="12" t="str">
+      <x:c r="O9" s="12" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
@@ -826,10 +798,7 @@
       <x:c r="N10" s="11" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="O10" s="10" t="str">
-        <x:v>使用系统下载的最新模板重新填写</x:v>
-      </x:c>
-      <x:c r="P10" s="12" t="str">
+      <x:c r="O10" s="12" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
@@ -876,10 +845,7 @@
       <x:c r="N11" s="11" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="O11" s="10" t="str">
-        <x:v>暂不重复导入，待系统修复后重试</x:v>
-      </x:c>
-      <x:c r="P11" s="12" t="str">
+      <x:c r="O11" s="12" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
@@ -896,7 +862,6 @@
     <x:col min="2" max="2" width="38" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="38" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -912,9 +877,6 @@
       <x:c r="D1" s="17" t="str">
         <x:v>示例</x:v>
       </x:c>
-      <x:c r="E1" s="17" t="str">
-        <x:v>处理口径</x:v>
-      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="10" t="str">
@@ -929,9 +891,6 @@
       <x:c r="D2" s="10" t="str">
         <x:v>缺少违约日列</x:v>
       </x:c>
-      <x:c r="E2" s="10" t="str">
-        <x:v>使用系统下载模板重新填写后导入</x:v>
-      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="10" t="str">
@@ -946,9 +905,6 @@
       <x:c r="D3" s="10" t="str">
         <x:v>订单编号、姓名、身份证号、债权金额为空</x:v>
       </x:c>
-      <x:c r="E3" s="10" t="str">
-        <x:v>补齐字段后重新导入</x:v>
-      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="10" t="str">
@@ -963,9 +919,6 @@
       <x:c r="D4" s="10" t="str">
         <x:v>身份证号不足18位</x:v>
       </x:c>
-      <x:c r="E4" s="10" t="str">
-        <x:v>修正字段格式后重新导入</x:v>
-      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="10" t="str">
@@ -980,9 +933,6 @@
       <x:c r="D5" s="10" t="str">
         <x:v>债权金额=-5999</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="str">
-        <x:v>修正金额后重新导入</x:v>
-      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="10" t="str">
@@ -997,9 +947,6 @@
       <x:c r="D6" s="10" t="str">
         <x:v>性别=未知</x:v>
       </x:c>
-      <x:c r="E6" s="10" t="str">
-        <x:v>按模板枚举填写</x:v>
-      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="10" t="str">
@@ -1014,9 +961,6 @@
       <x:c r="D7" s="10" t="str">
         <x:v>续租订单缺少父订单编号</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="str">
-        <x:v>补充主订单或修正父订单编号</x:v>
-      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="10" t="str">
@@ -1031,9 +975,6 @@
       <x:c r="D8" s="10" t="str">
         <x:v>已在DR202606100001导入</x:v>
       </x:c>
-      <x:c r="E8" s="10" t="str">
-        <x:v>以首次导入批次为准，本次跳过</x:v>
-      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="10" t="str">
@@ -1048,9 +989,6 @@
       <x:c r="D9" s="10" t="str">
         <x:v>已结清订单</x:v>
       </x:c>
-      <x:c r="E9" s="10" t="str">
-        <x:v>剔除或确认状态后重导</x:v>
-      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="10" t="str">
@@ -1064,9 +1002,6 @@
       </x:c>
       <x:c r="D10" s="10" t="str">
         <x:v>数据库写入失败</x:v>
-      </x:c>
-      <x:c r="E10" s="10" t="str">
-        <x:v>联系研发排查后重试</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1143,31 +1078,42 @@
         <x:v>案件生成</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>字段、金额、主续关系、订单状态校验通过后生成案件。</x:v>
+        <x:v>字段校验通过即可生成案件，案件立即生效并进入待委外队列。</x:v>
       </x:c>
       <x:c r="C6" s="10" t="str">
-        <x:v>材料齐套校验放二期。</x:v>
+        <x:v>二期材料导入不影响一期案件生效口径。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="10" t="str">
-        <x:v>重复订单</x:v>
+        <x:v>导出限制</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>历史批次已导入的订单本次跳过，并提示已存在批次号。</x:v>
+        <x:v>一期导入案件可进行后续法诉流程，但不支持导出要素表和导出法诉材料。</x:v>
       </x:c>
       <x:c r="C7" s="10" t="str">
-        <x:v>二期再评估覆盖和材料补充规则。</x:v>
+        <x:v>二期材料导入完成后再评估导出能力。</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="10" t="str">
+        <x:v>重复订单</x:v>
+      </x:c>
+      <x:c r="B8" s="10" t="str">
+        <x:v>历史批次已导入的订单本次跳过，并提示已存在批次号。</x:v>
+      </x:c>
+      <x:c r="C8" s="10" t="str">
+        <x:v>二期再评估覆盖和材料补充规则。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="10" t="str">
         <x:v>材料状态</x:v>
       </x:c>
-      <x:c r="B8" s="10" t="str">
+      <x:c r="B9" s="10" t="str">
         <x:v>一期不展示材料待处理、待补材料、未匹配材料池。</x:v>
       </x:c>
-      <x:c r="C8" s="10" t="str">
+      <x:c r="C9" s="10" t="str">
         <x:v>二期通过材料导入和处理详情承接。</x:v>
       </x:c>
     </x:row>
